--- a/documents/excel-equivalent/2. Emanating Request.xlsx
+++ b/documents/excel-equivalent/2. Emanating Request.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Patriach\Downloads\laravel\procurex\documents\excel-equivalent\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C3F4516-9EE5-47D6-9760-42B1AFEA9B00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6F6FF4D-7D35-45C9-89CC-3604F9E022BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -123,6 +123,39 @@
     </r>
   </si>
   <si>
+    <t>20 pcs</t>
+  </si>
+  <si>
+    <t>3 persons</t>
+  </si>
+  <si>
+    <t>50 pax</t>
+  </si>
+  <si>
+    <t>60 pcs</t>
+  </si>
+  <si>
+    <t>Training Kit</t>
+  </si>
+  <si>
+    <t>Honorarium for Resource Person</t>
+  </si>
+  <si>
+    <t>Meals &amp; Snacks (AM Snacks &amp; Lunch)</t>
+  </si>
+  <si>
+    <t>Tshirt with collar and print premium dry fit</t>
+  </si>
+  <si>
+    <t>ROMENTO R. MARASIGAN, DVM</t>
+  </si>
+  <si>
+    <t>PGDM</t>
+  </si>
+  <si>
+    <t>For use in the documentation of extension activities.</t>
+  </si>
+  <si>
     <r>
       <t xml:space="preserve">May I request for the purchase of supplies and materials needed by our department for the </t>
     </r>
@@ -166,41 +199,8 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> to wit:</t>
-    </r>
-  </si>
-  <si>
-    <t>20 pcs</t>
-  </si>
-  <si>
-    <t>3 persons</t>
-  </si>
-  <si>
-    <t>50 pax</t>
-  </si>
-  <si>
-    <t>60 pcs</t>
-  </si>
-  <si>
-    <t>Training Kit</t>
-  </si>
-  <si>
-    <t>Honorarium for Resource Person</t>
-  </si>
-  <si>
-    <t>Meals &amp; Snacks (AM Snacks &amp; Lunch)</t>
-  </si>
-  <si>
-    <t>Tshirt with collar and print premium dry fit</t>
-  </si>
-  <si>
-    <t>ROMENTO R. MARASIGAN, DVM</t>
-  </si>
-  <si>
-    <t>PGDM</t>
-  </si>
-  <si>
-    <t>For use in the documentation of extension activities.</t>
+      <t xml:space="preserve"> to with:</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -304,7 +304,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -670,7 +670,7 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -687,10 +687,10 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C17" s="6">
         <v>32000</v>
@@ -698,10 +698,10 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C18" s="6">
         <v>15000</v>
@@ -709,10 +709,10 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C19" s="6">
         <v>35000</v>
@@ -720,10 +720,10 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C20" s="6">
         <v>48000</v>
@@ -752,20 +752,21 @@
         <v>16</v>
       </c>
       <c r="B27" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C29" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C30" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>